--- a/artfynd/A 53670-2021 artfynd.xlsx
+++ b/artfynd/A 53670-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53670-2021 artfynd.xlsx
+++ b/artfynd/A 53670-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106691512</v>
+        <v>106693800</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrskog vid södra Tokarpsmossen, nära Trollebo hål, Sm</t>
+          <t>Aspbestånd precis N om riksväg 31, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460347.6988597194</v>
+        <v>460255</v>
       </c>
       <c r="R2" t="n">
-        <v>6398907.32957205</v>
+        <v>6398792</v>
       </c>
       <c r="S2" t="n">
         <v>16</v>
@@ -766,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,12 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Avverkningsanmälan: A 53670-2021 Området år delvis påverkat av tidigare mänsklig aktivitet, som ett spår efter skogsmaskin. Annars finns flera äldre granar och tallar och tjocka mosstäcken. Orkidéerna är dock begränsade till områdets norra del, möjligtvis då den södra gränsar till ett kalhygge med unga granar.</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +765,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -809,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106690519</v>
+        <v>106690447</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,7 +813,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrskog vid södra Tokarpsmossen , Sm</t>
+          <t>Barrskog vid södra Tokarpsmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460415.4742889123</v>
+        <v>460453</v>
       </c>
       <c r="R3" t="n">
-        <v>6398999.041606329</v>
+        <v>6399071</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -943,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106691492</v>
+        <v>106690519</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +942,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -995,17 +959,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog vid södra Tokarpsmossen, nära Trollebo hål, Sm</t>
+          <t>Barrskog vid södra Tokarpsmossen , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460356.3157355384</v>
+        <v>460415</v>
       </c>
       <c r="R4" t="n">
-        <v>6398858.652432495</v>
+        <v>6399000</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1074,6 +1038,264 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106691492</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog vid södra Tokarpsmossen, nära Trollebo hål, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>460357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398858</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Öggestorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avverkningsanmälan: A 53670-2021 Området år delvis påverkat av tidigare mänsklig aktivitet, som ett spår efter skogsmaskin. Annars finns flera äldre granar och tallar och tjocka mosstäcken. Orkidéerna är dock begränsade till områdets norra del, möjligtvis då den södra gränsar till ett kalhygge med unga granar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106691512</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barrskog vid södra Tokarpsmossen, nära Trollebo hål, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>460348</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398907</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Öggestorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Avverkningsanmälan: A 53670-2021 Området år delvis påverkat av tidigare mänsklig aktivitet, som ett spår efter skogsmaskin. Annars finns flera äldre granar och tallar och tjocka mosstäcken. Orkidéerna är dock begränsade till områdets norra del, möjligtvis då den södra gränsar till ett kalhygge med unga granar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53670-2021 artfynd.xlsx
+++ b/artfynd/A 53670-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106693800</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106690447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106690519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106691492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1296,8 +1321,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106691512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>